--- a/conformance/fixtures/040-list-sheet-hidden-states-removed/template.xlsx
+++ b/conformance/fixtures/040-list-sheet-hidden-states-removed/template.xlsx
@@ -4,17 +4,16 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="_config" state="hidden" r:id="rId4"/>
+    <sheet sheetId="1" name="__config__" state="hidden" r:id="rId4"/>
     <sheet sheetId="2" name="Report" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="_Allowed" state="hidden" r:id="rId6"/>
-    <sheet sheetId="4" name="_Excluded" state="veryHidden" r:id="rId7"/>
+    <sheet sheetId="3" name="__lists__" state="veryHidden" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>name</t>
   </si>
@@ -46,7 +45,10 @@
     <t>Amount</t>
   </si>
   <si>
-    <t>{{ @filter [Customer] in _Allowed }}</t>
+    <t>{{ @filter [Customer] in __lists__[Allowed] }}</t>
+  </si>
+  <si>
+    <t>{{ @filter [Customer] !in __lists__[Excluded] }}</t>
   </si>
   <si>
     <t>{{ [Customer] }}</t>
@@ -55,13 +57,19 @@
     <t>{{ [Amount] }}</t>
   </si>
   <si>
+    <t>Allowed</t>
+  </si>
+  <si>
+    <t>Excluded</t>
+  </si>
+  <si>
     <t>Acme</t>
   </si>
   <si>
+    <t>Gamma</t>
+  </si>
+  <si>
     <t>Beta</t>
-  </si>
-  <si>
-    <t>Gamma</t>
   </si>
 </sst>
 </file>
@@ -481,65 +489,65 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
